--- a/data/availability/projects/qatari-diar/alam-al-roum.xlsx
+++ b/data/availability/projects/qatari-diar/alam-al-roum.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
